--- a/output_template/Soil_Infiltration_FieldData_template.xlsx
+++ b/output_template/Soil_Infiltration_FieldData_template.xlsx
@@ -15,10 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t xml:space="preserve">Site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subplot</t>
+    <t xml:space="preserve">SoilType</t>
   </si>
   <si>
     <t xml:space="preserve">SuctionRate</t>
@@ -31,6 +28,9 @@
   </si>
   <si>
     <t xml:space="preserve">SoilMoisture_12cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group</t>
   </si>
 </sst>
 </file>
@@ -38,19 +38,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -61,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -69,18 +63,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -370,56 +358,50 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"PSAM,THSL,TCAM,THCL,TCAL"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B201</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"0.5,1,2,3,4,5,6,7"</xm:f>
-          </x14:formula1>
-          <xm:sqref>C2:C201</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -427,55 +409,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"PSAM,THSL,TCAM,THCL,TCAL"</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B201</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"0.5,1,2,3,4,5,6,7"</xm:f>
-          </x14:formula1>
-          <xm:sqref>C2:C201</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>